--- a/data/trans_orig/IQ17B_M_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ17B_M_R-Provincia-trans_orig.xlsx
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,54; 7,08</t>
+          <t>4,34; 6,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,59; 6,71</t>
+          <t>3,53; 6,63</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,98; 7,5</t>
+          <t>4,8; 7,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 6,48</t>
+          <t>3,89; 6,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 8,98</t>
+          <t>3,94; 8,97</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,7; 6,48</t>
+          <t>3,71; 6,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 8,46</t>
+          <t>4,91; 8,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,6</t>
+          <t>4,32; 7,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,55; 7,46</t>
+          <t>4,64; 7,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,87; 5,94</t>
+          <t>3,89; 5,89</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 7,42</t>
+          <t>5,21; 7,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,33; 6,44</t>
+          <t>4,31; 6,35</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,96; 7,12</t>
+          <t>4,97; 7,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 4,81</t>
+          <t>3,15; 4,8</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,24; 8,82</t>
+          <t>5,18; 8,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,43; 10,66</t>
+          <t>6,35; 11,06</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 8,82</t>
+          <t>5,84; 9,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,68; 8,54</t>
+          <t>4,74; 8,95</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,28; 9,99</t>
+          <t>6,34; 10,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,71; 7,09</t>
+          <t>4,81; 7,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 7,44</t>
+          <t>5,64; 7,35</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,12; 6,18</t>
+          <t>4,15; 6,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,11; 8,64</t>
+          <t>6,24; 8,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,75; 8,1</t>
+          <t>5,8; 8,11</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,28; 12,3</t>
+          <t>5,33; 11,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 5,7</t>
+          <t>3,69; 5,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,91; 7,6</t>
+          <t>4,89; 7,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,57; 9,24</t>
+          <t>5,52; 9,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,5; 5,53</t>
+          <t>3,52; 5,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,62; 7,16</t>
+          <t>4,56; 7,01</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,36; 8,93</t>
+          <t>6,4; 8,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,06; 11,47</t>
+          <t>6,83; 11,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,86</t>
+          <t>4,63; 8,18</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 6,09</t>
+          <t>4,39; 5,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,79</t>
+          <t>5,9; 7,88</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,76; 9,44</t>
+          <t>6,73; 9,52</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,08; 10,61</t>
+          <t>5,07; 10,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,53; 7,55</t>
+          <t>4,58; 7,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4,99; 10,27</t>
+          <t>5,0; 10,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,57; 17,46</t>
+          <t>5,34; 17,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,39; 8,21</t>
+          <t>5,26; 8,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,44; 10,44</t>
+          <t>6,51; 10,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,57; 8,29</t>
+          <t>4,59; 8,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,28; 19,57</t>
+          <t>7,74; 20,1</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,53; 8,56</t>
+          <t>5,51; 8,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,97; 8,53</t>
+          <t>5,95; 8,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,19; 8,41</t>
+          <t>5,06; 8,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,43; 16,62</t>
+          <t>7,18; 16,33</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,71; 18,07</t>
+          <t>5,61; 17,61</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,9; 6,21</t>
+          <t>2,78; 6,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,54; 11,76</t>
+          <t>5,49; 11,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,87; 9,86</t>
+          <t>5,99; 9,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,22; 10,51</t>
+          <t>5,17; 10,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,16; 5,56</t>
+          <t>3,15; 5,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,4; 11,47</t>
+          <t>5,45; 11,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,86; 11,52</t>
+          <t>7,72; 11,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,98; 11,77</t>
+          <t>6,1; 12,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,3; 5,26</t>
+          <t>3,28; 5,33</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,01; 10,61</t>
+          <t>5,94; 10,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,35; 9,93</t>
+          <t>7,4; 9,82</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,34; 7,86</t>
+          <t>4,26; 7,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,86; 4,68</t>
+          <t>2,91; 4,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,7; 10,38</t>
+          <t>6,62; 10,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,74; 14,82</t>
+          <t>9,61; 14,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,51; 6,11</t>
+          <t>3,47; 5,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,33; 7,88</t>
+          <t>4,28; 7,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,36; 8,59</t>
+          <t>5,42; 8,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,39; 14,42</t>
+          <t>9,26; 14,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,1; 6,19</t>
+          <t>4,15; 6,41</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,85; 5,92</t>
+          <t>3,86; 5,93</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,31; 8,63</t>
+          <t>6,37; 8,59</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>9,85; 13,33</t>
+          <t>10,09; 13,57</t>
         </is>
       </c>
     </row>
@@ -1556,27 +1556,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,17; 8,46</t>
+          <t>5,27; 8,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,03; 8,3</t>
+          <t>5,15; 8,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,53; 7,55</t>
+          <t>5,45; 7,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,49; 6,99</t>
+          <t>4,61; 6,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,31; 7,82</t>
+          <t>5,28; 7,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,95; 8,98</t>
+          <t>6,0; 8,83</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,16; 19,65</t>
+          <t>5,97; 19,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,5; 7,53</t>
+          <t>5,52; 7,55</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,03; 6,85</t>
+          <t>5,05; 6,72</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5,99; 7,78</t>
+          <t>6,02; 7,82</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,88; 12,52</t>
+          <t>5,85; 13,53</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,54; 7,48</t>
+          <t>5,58; 7,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,4; 7,14</t>
+          <t>5,44; 7,09</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,8; 5,28</t>
+          <t>3,8; 5,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,18; 12,01</t>
+          <t>10,11; 11,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,64; 9,51</t>
+          <t>6,48; 9,39</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,28; 8,9</t>
+          <t>5,28; 9,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,83; 5,24</t>
+          <t>3,79; 5,13</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,75; 12,82</t>
+          <t>10,72; 12,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,32; 8,07</t>
+          <t>6,34; 8,06</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,63; 7,41</t>
+          <t>5,55; 7,46</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3,99; 4,97</t>
+          <t>4,02; 5,03</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,76; 12,08</t>
+          <t>10,66; 12,08</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,06</t>
+          <t>5,83; 7,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,78; 5,67</t>
+          <t>4,81; 5,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,65; 6,65</t>
+          <t>5,62; 6,64</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,46; 8,98</t>
+          <t>7,55; 8,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,81; 6,88</t>
+          <t>5,8; 6,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,44; 6,63</t>
+          <t>5,42; 6,61</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,88; 6,97</t>
+          <t>5,9; 6,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,53; 11,4</t>
+          <t>8,48; 11,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,95; 6,85</t>
+          <t>5,95; 6,81</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5,26; 6,05</t>
+          <t>5,22; 5,96</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,93; 6,67</t>
+          <t>5,91; 6,65</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,18; 9,71</t>
+          <t>8,21; 9,77</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ17B_M_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IQ17B_M_R-Provincia-trans_orig.xlsx
@@ -526,13 +526,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores en función del número de meses de su última consulta al médico (tasa de respuesta: 91,3%)</t>
+          <t>Tiempo medio en meses desde la última consulta médica por algo que le pasaba a su hijo/a (tasa de respuesta: 91,3%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5,58</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,82</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,19</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5,47</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>5,46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,57</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>6,07</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,81</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>5,58</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,82</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,19</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>5,49</t>
+          <t>4,53</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,16</t>
+          <t>5,03</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 6,95</t>
+          <t>4,13; 8,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,53; 6,63</t>
+          <t>3,68; 6,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,8; 7,41</t>
+          <t>4,74; 8,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 6,42</t>
+          <t>4,11; 7,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,94; 8,97</t>
+          <t>4,48; 7,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 6,42</t>
+          <t>3,52; 6,56</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 8,46</t>
+          <t>4,94; 7,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,32; 7,48</t>
+          <t>3,86; 5,53</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,64; 7,26</t>
+          <t>4,56; 7,26</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3,89; 5,89</t>
+          <t>3,93; 5,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5,21; 7,49</t>
+          <t>5,19; 7,4</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 6,35</t>
+          <t>4,31; 6,27</t>
         </is>
       </c>
     </row>
@@ -788,42 +788,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>6,83</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,01</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>7,83</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5,85</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>5,86</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>3,79</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>6,63</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,86</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>6,83</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,01</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>7,83</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>5,79</t>
+          <t>7,99</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6,72</t>
+          <t>6,84</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,97; 7,04</t>
+          <t>5,83; 8,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,15; 4,8</t>
+          <t>4,75; 8,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,18; 8,59</t>
+          <t>6,47; 10,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,35; 11,06</t>
+          <t>4,71; 7,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,84; 9,06</t>
+          <t>4,96; 7,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 8,95</t>
+          <t>3,07; 4,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,34; 10,0</t>
+          <t>5,2; 8,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,81; 7,21</t>
+          <t>6,41; 11,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,64; 7,35</t>
+          <t>5,62; 7,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,15; 6,33</t>
+          <t>4,14; 6,23</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6,24; 8,76</t>
+          <t>6,08; 8,79</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,8; 8,11</t>
+          <t>5,94; 8,42</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,25</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5,61</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>7,54</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8,93</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>6,97</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>4,44</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>6,03</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>7,01</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,25</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,61</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,54</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>8,7</t>
+          <t>7,15</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>7,94</t>
+          <t>8,09</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,33; 11,91</t>
+          <t>3,51; 5,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,69; 5,8</t>
+          <t>4,52; 7,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,89; 7,68</t>
+          <t>6,37; 9,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,52; 9,34</t>
+          <t>7,12; 11,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,52; 5,24</t>
+          <t>5,1; 11,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,56; 7,01</t>
+          <t>3,7; 5,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,4; 8,96</t>
+          <t>4,8; 7,54</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,83; 11,12</t>
+          <t>5,6; 9,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,63; 8,18</t>
+          <t>4,67; 8,08</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4,39; 5,99</t>
+          <t>4,28; 5,95</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5,9; 7,88</t>
+          <t>5,86; 7,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>6,73; 9,52</t>
+          <t>6,69; 9,62</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>6,51</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>8,18</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,19</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12,94</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>6,54</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>5,77</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>6,67</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8,61</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>6,51</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,18</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,19</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>13,25</t>
+          <t>8,66</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>11,15</t>
+          <t>10,88</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,07; 10,5</t>
+          <t>5,18; 8,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,58; 7,66</t>
+          <t>6,43; 10,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,0; 10,23</t>
+          <t>4,55; 8,27</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5,34; 17,5</t>
+          <t>7,37; 19,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 8,26</t>
+          <t>5,11; 10,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,51; 10,48</t>
+          <t>4,65; 7,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 8,56</t>
+          <t>4,93; 9,81</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7,74; 20,1</t>
+          <t>5,64; 16,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5,51; 8,36</t>
+          <t>5,52; 8,37</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,95; 8,34</t>
+          <t>5,9; 8,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,2</t>
+          <t>5,2; 8,32</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,18; 16,33</t>
+          <t>7,6; 16,1</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,05</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>4,1</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,65</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>9,35</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>8,69</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>4,05</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>7,56</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,58</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>7,05</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>4,1</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,65</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,44</t>
+          <t>7,69</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8,58</t>
+          <t>8,55</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,61; 17,61</t>
+          <t>5,24; 10,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,78; 6,38</t>
+          <t>3,2; 5,51</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,49; 11,46</t>
+          <t>5,42; 12,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5,99; 9,74</t>
+          <t>7,67; 11,34</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,17; 10,14</t>
+          <t>5,72; 18,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,15; 5,52</t>
+          <t>2,85; 6,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,45; 11,85</t>
+          <t>5,57; 11,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,72; 11,43</t>
+          <t>6,24; 9,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,1; 12,36</t>
+          <t>6,05; 12,03</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,33</t>
+          <t>3,3; 5,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5,94; 10,44</t>
+          <t>5,98; 10,28</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>7,4; 9,82</t>
+          <t>7,33; 9,99</t>
         </is>
       </c>
     </row>
@@ -1348,42 +1348,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4,38</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5,66</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>6,67</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11,7</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>5,62</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>3,62</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>8,18</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11,74</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>4,38</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5,66</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>6,67</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>11,41</t>
+          <t>12,08</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>11,57</t>
+          <t>11,9</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,26; 7,9</t>
+          <t>3,43; 5,88</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,91; 4,79</t>
+          <t>4,11; 7,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,62; 10,08</t>
+          <t>5,45; 8,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,61; 14,74</t>
+          <t>9,51; 14,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,47; 5,81</t>
+          <t>4,15; 8,04</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,28; 7,65</t>
+          <t>2,92; 4,78</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,42; 8,73</t>
+          <t>6,66; 9,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,26; 14,41</t>
+          <t>9,44; 14,88</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,15; 6,41</t>
+          <t>4,11; 6,45</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3,86; 5,93</t>
+          <t>3,9; 6,01</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6,37; 8,59</t>
+          <t>6,4; 8,75</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,09; 13,57</t>
+          <t>10,15; 13,79</t>
         </is>
       </c>
     </row>
@@ -1488,42 +1488,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>6,4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5,34</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>7,11</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>10,52</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>6,42</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>6,01</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>6,4</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,62</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>6,4</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,34</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>7,11</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>10,54</t>
+          <t>5,8</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,05</t>
+          <t>7,96</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,27; 8,48</t>
+          <t>5,33; 7,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,15; 8,47</t>
+          <t>4,63; 6,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,45; 7,58</t>
+          <t>6,05; 8,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4,61; 6,91</t>
+          <t>6,46; 19,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,28; 7,88</t>
+          <t>5,2; 8,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,62; 6,17</t>
+          <t>5,13; 8,28</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,0; 8,83</t>
+          <t>5,51; 7,54</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,97; 19,83</t>
+          <t>4,76; 7,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,52; 7,55</t>
+          <t>5,63; 7,68</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5,05; 6,72</t>
+          <t>5,06; 6,74</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>6,02; 7,82</t>
+          <t>6,01; 7,79</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,85; 13,53</t>
+          <t>6,11; 12,65</t>
         </is>
       </c>
     </row>
@@ -1628,42 +1628,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>7,64</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>6,31</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4,44</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>11,8</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>6,46</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>6,19</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>4,4</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>11,0</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>7,64</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>6,31</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>4,44</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>11,69</t>
+          <t>11,11</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11,37</t>
+          <t>11,47</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,58; 7,55</t>
+          <t>6,59; 9,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,44; 7,09</t>
+          <t>5,29; 9,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,8; 5,27</t>
+          <t>3,85; 5,2</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,11; 11,87</t>
+          <t>10,78; 12,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,48; 9,39</t>
+          <t>5,69; 7,61</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,28; 9,08</t>
+          <t>5,5; 7,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,79; 5,13</t>
+          <t>3,83; 5,28</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>10,72; 12,66</t>
+          <t>10,22; 12,11</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>6,34; 8,06</t>
+          <t>6,34; 8,01</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5,55; 7,46</t>
+          <t>5,55; 7,45</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4,02; 5,03</t>
+          <t>3,96; 4,97</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>10,66; 12,08</t>
+          <t>10,77; 12,13</t>
         </is>
       </c>
     </row>
@@ -1768,42 +1768,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>6,31</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5,93</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6,41</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>9,63</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>6,38</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>5,19</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>6,11</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>8,13</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>6,31</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5,93</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>6,41</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>9,47</t>
+          <t>8,4</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,84</t>
+          <t>9,03</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5,83; 7,15</t>
+          <t>5,82; 6,89</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4,81; 5,72</t>
+          <t>5,39; 6,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,62; 6,64</t>
+          <t>5,91; 6,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7,55; 8,97</t>
+          <t>8,66; 11,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>5,8; 6,94</t>
+          <t>5,86; 7,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,42; 6,61</t>
+          <t>4,77; 5,69</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,9; 6,98</t>
+          <t>5,65; 6,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>8,48; 11,31</t>
+          <t>7,81; 9,31</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5,95; 6,81</t>
+          <t>5,96; 6,81</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>5,22; 5,96</t>
+          <t>5,25; 6,01</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>5,91; 6,65</t>
+          <t>5,89; 6,62</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>8,21; 9,77</t>
+          <t>8,42; 9,85</t>
         </is>
       </c>
     </row>
